--- a/converted/tozalangan/chinobod/Sentabr 10 kunlik/Elektr Qoidabuzarliklar.xlsx
+++ b/converted/tozalangan/chinobod/Sentabr 10 kunlik/Elektr Qoidabuzarliklar.xlsx
@@ -11,11 +11,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="149">
   <si>
     <t>Qoidabuzarliklar Sentabr (1–10) Holatiga Ko'ra</t>
   </si>
   <si>
+    <t>Podstansiya</t>
+  </si>
+  <si>
+    <t>Fider</t>
+  </si>
+  <si>
     <t>TP Nomi</t>
   </si>
   <si>
@@ -55,6 +61,12 @@
     <t>Manba (fayl, qator)</t>
   </si>
   <si>
+    <t>Qo'shtepasaroy</t>
+  </si>
+  <si>
+    <t>Sirmoq</t>
+  </si>
+  <si>
     <t>136</t>
   </si>
   <si>
@@ -82,6 +94,12 @@
     <t>chinobod/Elektr Qoidabuzarliklar.xlsx [Sentabr], 3-qator</t>
   </si>
   <si>
+    <t>Chinobod</t>
+  </si>
+  <si>
+    <t>Kamoliy</t>
+  </si>
+  <si>
     <t>100</t>
   </si>
   <si>
@@ -100,6 +118,9 @@
     <t>chinobod/Elektr Qoidabuzarliklar.xlsx [Sentabr], 4-qator</t>
   </si>
   <si>
+    <t>Qaxramon</t>
+  </si>
+  <si>
     <t>61</t>
   </si>
   <si>
@@ -115,6 +136,9 @@
     <t>chinobod/Elektr Qoidabuzarliklar.xlsx [Sentabr], 5-qator</t>
   </si>
   <si>
+    <t>Yangiqishloq</t>
+  </si>
+  <si>
     <t>152</t>
   </si>
   <si>
@@ -169,6 +193,9 @@
     <t>chinobod/Elektr Qoidabuzarliklar.xlsx [Sentabr], 8-qator</t>
   </si>
   <si>
+    <t>Xaqulobod</t>
+  </si>
+  <si>
     <t>190</t>
   </si>
   <si>
@@ -217,6 +244,9 @@
     <t>chinobod/Elektr Qoidabuzarliklar.xlsx [Sentabr], 11-qator</t>
   </si>
   <si>
+    <t>Qiyali</t>
+  </si>
+  <si>
     <t>336</t>
   </si>
   <si>
@@ -299,6 +329,12 @@
   </si>
   <si>
     <t>chinobod/Elektr Qoidabuzarliklar.xlsx [Sentabr], 16-qator</t>
+  </si>
+  <si>
+    <t>Oltinko'l</t>
+  </si>
+  <si>
+    <t>Alpomish</t>
   </si>
   <si>
     <t>174</t>
@@ -840,18 +876,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="14" style="1" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
-    <col min="6" max="7" width="18" style="2" customWidth="1"/>
-    <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="9" max="13" width="26" customWidth="1"/>
+    <col min="1" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="14" style="1" customWidth="1"/>
+    <col min="7" max="7" width="34" customWidth="1"/>
+    <col min="8" max="9" width="18" style="2" customWidth="1"/>
+    <col min="10" max="10" width="22" customWidth="1"/>
+    <col min="11" max="15" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -867,8 +903,10 @@
       <c r="K1"/>
       <c r="L1"/>
       <c r="M1"/>
-    </row>
-    <row r="2" ht="45" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N1"/>
+      <c r="O1"/>
+    </row>
+    <row r="2" ht="45" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -893,10 +931,10 @@
       <c r="H2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="4" t="s">
         <v>10</v>
       </c>
       <c r="K2" s="5" t="s">
@@ -908,884 +946,1028 @@
       <c r="M2" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="1">
+        <v>46267</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="2">
+        <v>149500</v>
+      </c>
+      <c r="I3" s="2">
+        <v>230</v>
+      </c>
+      <c r="J3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="1">
+        <v>46267</v>
+      </c>
+      <c r="G4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="2">
+        <v>112600</v>
+      </c>
+      <c r="I4" s="2">
+        <v>173</v>
+      </c>
+      <c r="J4" t="s">
+        <v>22</v>
+      </c>
+      <c r="L4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" t="s">
+        <v>33</v>
+      </c>
+      <c r="N4" t="s">
+        <v>25</v>
+      </c>
+      <c r="O4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="1">
+      <c r="B5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="1">
         <v>46267</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" s="2">
+        <v>112600</v>
+      </c>
+      <c r="I5" s="2">
+        <v>173</v>
+      </c>
+      <c r="J5" t="s">
+        <v>22</v>
+      </c>
+      <c r="L5" t="s">
+        <v>39</v>
+      </c>
+      <c r="N5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="1">
+        <v>46267</v>
+      </c>
+      <c r="G6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" s="2">
+        <v>327600</v>
+      </c>
+      <c r="I6" s="2">
+        <v>504</v>
+      </c>
+      <c r="J6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" t="s">
+        <v>45</v>
+      </c>
+      <c r="M6" t="s">
+        <v>46</v>
+      </c>
+      <c r="N6" t="s">
+        <v>25</v>
+      </c>
+      <c r="O6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="1">
+        <v>46268</v>
+      </c>
+      <c r="G7" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7" s="2">
+        <v>152750</v>
+      </c>
+      <c r="I7" s="2">
+        <v>235</v>
+      </c>
+      <c r="J7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" t="s">
+        <v>51</v>
+      </c>
+      <c r="L7" t="s">
+        <v>52</v>
+      </c>
+      <c r="N7" t="s">
+        <v>25</v>
+      </c>
+      <c r="O7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" s="1">
+        <v>46268</v>
+      </c>
+      <c r="G8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H8" s="2">
+        <v>190300</v>
+      </c>
+      <c r="I8" s="2">
+        <v>173</v>
+      </c>
+      <c r="J8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L8" t="s">
+        <v>57</v>
+      </c>
+      <c r="M8" t="s">
+        <v>58</v>
+      </c>
+      <c r="N8" t="s">
+        <v>25</v>
+      </c>
+      <c r="O8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" s="1">
+        <v>46269</v>
+      </c>
+      <c r="G9" t="s">
+        <v>63</v>
+      </c>
+      <c r="H9" s="2">
+        <v>1409100</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1281</v>
+      </c>
+      <c r="J9" t="s">
+        <v>22</v>
+      </c>
+      <c r="L9" t="s">
+        <v>64</v>
+      </c>
+      <c r="N9" t="s">
+        <v>25</v>
+      </c>
+      <c r="O9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="1">
+        <v>46270</v>
+      </c>
+      <c r="G10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H10" s="2">
+        <v>568100</v>
+      </c>
+      <c r="I10" s="2">
+        <v>874</v>
+      </c>
+      <c r="J10" t="s">
+        <v>22</v>
+      </c>
+      <c r="K10" t="s">
+        <v>69</v>
+      </c>
+      <c r="L10" t="s">
+        <v>70</v>
+      </c>
+      <c r="M10" t="s">
+        <v>71</v>
+      </c>
+      <c r="N10" t="s">
+        <v>25</v>
+      </c>
+      <c r="O10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="1">
+        <v>46272</v>
+      </c>
+      <c r="G11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" s="2">
+        <v>98800</v>
+      </c>
+      <c r="I11" s="2">
+        <v>152</v>
+      </c>
+      <c r="J11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L11" t="s">
+        <v>75</v>
+      </c>
+      <c r="M11" t="s">
+        <v>33</v>
+      </c>
+      <c r="N11" t="s">
+        <v>25</v>
+      </c>
+      <c r="O11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="1">
+        <v>46272</v>
+      </c>
+      <c r="G12" t="s">
+        <v>80</v>
+      </c>
+      <c r="H12" s="2">
+        <v>112600</v>
+      </c>
+      <c r="I12" s="2">
+        <v>173.23076923076923</v>
+      </c>
+      <c r="J12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L12" t="s">
+        <v>81</v>
+      </c>
+      <c r="N12" t="s">
+        <v>25</v>
+      </c>
+      <c r="O12" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="2">
-        <v>149500</v>
-      </c>
-      <c r="G3" s="2">
-        <v>230</v>
-      </c>
-      <c r="H3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="C13" t="s">
+        <v>83</v>
+      </c>
+      <c r="D13" t="s">
+        <v>84</v>
+      </c>
+      <c r="E13" t="s">
         <v>20</v>
       </c>
-      <c r="L3" t="s">
+      <c r="F13" s="1">
+        <v>46272</v>
+      </c>
+      <c r="G13" t="s">
+        <v>85</v>
+      </c>
+      <c r="H13" s="2">
+        <v>346450</v>
+      </c>
+      <c r="I13" s="2">
+        <v>533</v>
+      </c>
+      <c r="J13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" t="s">
+        <v>86</v>
+      </c>
+      <c r="L13" t="s">
+        <v>87</v>
+      </c>
+      <c r="N13" t="s">
+        <v>25</v>
+      </c>
+      <c r="O13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" t="s">
+        <v>89</v>
+      </c>
+      <c r="D14" t="s">
+        <v>90</v>
+      </c>
+      <c r="E14" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="1">
+        <v>46272</v>
+      </c>
+      <c r="G14" t="s">
         <v>21</v>
       </c>
-      <c r="M3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="H14" s="2">
+        <v>5230550</v>
+      </c>
+      <c r="I14" s="2">
+        <v>8047</v>
+      </c>
+      <c r="J14" t="s">
+        <v>22</v>
+      </c>
+      <c r="L14" t="s">
+        <v>91</v>
+      </c>
+      <c r="N14" t="s">
+        <v>25</v>
+      </c>
+      <c r="O14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D15" t="s">
+        <v>94</v>
+      </c>
+      <c r="E15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15" s="1">
+        <v>46272</v>
+      </c>
+      <c r="G15" t="s">
+        <v>95</v>
+      </c>
+      <c r="H15" s="2">
+        <v>2956800</v>
+      </c>
+      <c r="I15" s="2">
+        <v>2688</v>
+      </c>
+      <c r="J15" t="s">
+        <v>22</v>
+      </c>
+      <c r="L15" t="s">
+        <v>96</v>
+      </c>
+      <c r="M15" t="s">
+        <v>97</v>
+      </c>
+      <c r="N15" t="s">
+        <v>25</v>
+      </c>
+      <c r="O15" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" t="s">
+        <v>99</v>
+      </c>
+      <c r="D16" t="s">
+        <v>100</v>
+      </c>
+      <c r="E16" t="s">
+        <v>55</v>
+      </c>
+      <c r="F16" s="1">
+        <v>46273</v>
+      </c>
+      <c r="G16" t="s">
+        <v>101</v>
+      </c>
+      <c r="H16" s="2">
+        <v>4514400</v>
+      </c>
+      <c r="I16" s="2">
+        <v>4104</v>
+      </c>
+      <c r="J16" t="s">
+        <v>22</v>
+      </c>
+      <c r="K16" t="s">
+        <v>102</v>
+      </c>
+      <c r="L16" t="s">
+        <v>103</v>
+      </c>
+      <c r="M16" t="s">
+        <v>104</v>
+      </c>
+      <c r="N16" t="s">
+        <v>25</v>
+      </c>
+      <c r="O16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>106</v>
+      </c>
+      <c r="B17" t="s">
+        <v>107</v>
+      </c>
+      <c r="C17" t="s">
+        <v>108</v>
+      </c>
+      <c r="D17" t="s">
+        <v>109</v>
+      </c>
+      <c r="E17" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="1">
+        <v>46273</v>
+      </c>
+      <c r="G17" t="s">
+        <v>31</v>
+      </c>
+      <c r="H17" s="2">
+        <v>318500</v>
+      </c>
+      <c r="I17" s="2">
+        <v>490</v>
+      </c>
+      <c r="J17" t="s">
+        <v>22</v>
+      </c>
+      <c r="K17" t="s">
+        <v>110</v>
+      </c>
+      <c r="L17" t="s">
+        <v>111</v>
+      </c>
+      <c r="M17" t="s">
+        <v>33</v>
+      </c>
+      <c r="N17" t="s">
+        <v>25</v>
+      </c>
+      <c r="O17" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="1">
-        <v>46267</v>
-      </c>
-      <c r="E4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="2">
-        <v>112600</v>
-      </c>
-      <c r="G4" s="2">
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
+        <v>113</v>
+      </c>
+      <c r="D18" t="s">
+        <v>114</v>
+      </c>
+      <c r="E18" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" s="1">
+        <v>46274</v>
+      </c>
+      <c r="G18" t="s">
+        <v>31</v>
+      </c>
+      <c r="H18" s="2">
+        <v>207350</v>
+      </c>
+      <c r="I18" s="2">
+        <v>319</v>
+      </c>
+      <c r="J18" t="s">
+        <v>22</v>
+      </c>
+      <c r="L18" t="s">
+        <v>115</v>
+      </c>
+      <c r="M18" t="s">
+        <v>33</v>
+      </c>
+      <c r="N18" t="s">
+        <v>25</v>
+      </c>
+      <c r="O18" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" t="s">
+        <v>117</v>
+      </c>
+      <c r="D19" t="s">
+        <v>118</v>
+      </c>
+      <c r="E19" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" s="1">
+        <v>46274</v>
+      </c>
+      <c r="G19" t="s">
+        <v>119</v>
+      </c>
+      <c r="H19" s="2">
+        <v>112450</v>
+      </c>
+      <c r="I19" s="2">
         <v>173</v>
       </c>
-      <c r="H4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K4" t="s">
-        <v>27</v>
-      </c>
-      <c r="L4" t="s">
-        <v>21</v>
-      </c>
-      <c r="M4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="J19" t="s">
+        <v>22</v>
+      </c>
+      <c r="K19" t="s">
+        <v>120</v>
+      </c>
+      <c r="L19" t="s">
+        <v>121</v>
+      </c>
+      <c r="M19" t="s">
+        <v>122</v>
+      </c>
+      <c r="N19" t="s">
+        <v>25</v>
+      </c>
+      <c r="O19" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="1">
-        <v>46267</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="B20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20" s="1">
+        <v>46274</v>
+      </c>
+      <c r="G20" t="s">
+        <v>85</v>
+      </c>
+      <c r="H20" s="2">
+        <v>185900</v>
+      </c>
+      <c r="I20" s="2">
+        <v>286</v>
+      </c>
+      <c r="J20" t="s">
+        <v>22</v>
+      </c>
+      <c r="K20" t="s">
+        <v>86</v>
+      </c>
+      <c r="L20" t="s">
+        <v>124</v>
+      </c>
+      <c r="M20" t="s">
+        <v>125</v>
+      </c>
+      <c r="N20" t="s">
+        <v>25</v>
+      </c>
+      <c r="O20" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>106</v>
+      </c>
+      <c r="B21" t="s">
+        <v>107</v>
+      </c>
+      <c r="C21" t="s">
+        <v>127</v>
+      </c>
+      <c r="D21" t="s">
+        <v>128</v>
+      </c>
+      <c r="E21" t="s">
+        <v>20</v>
+      </c>
+      <c r="F21" s="1">
+        <v>46275</v>
+      </c>
+      <c r="G21" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="2">
-        <v>112600</v>
-      </c>
-      <c r="G5" s="2">
+      <c r="H21" s="2">
+        <v>261950</v>
+      </c>
+      <c r="I21" s="2">
+        <v>403</v>
+      </c>
+      <c r="J21" t="s">
+        <v>22</v>
+      </c>
+      <c r="K21" t="s">
+        <v>129</v>
+      </c>
+      <c r="L21" t="s">
+        <v>130</v>
+      </c>
+      <c r="M21" t="s">
+        <v>33</v>
+      </c>
+      <c r="N21" t="s">
+        <v>25</v>
+      </c>
+      <c r="O21" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" t="s">
+        <v>132</v>
+      </c>
+      <c r="D22" t="s">
+        <v>133</v>
+      </c>
+      <c r="E22" t="s">
+        <v>20</v>
+      </c>
+      <c r="F22" s="1">
+        <v>46275</v>
+      </c>
+      <c r="G22" t="s">
+        <v>31</v>
+      </c>
+      <c r="H22" s="2">
+        <v>112450</v>
+      </c>
+      <c r="I22" s="2">
         <v>173</v>
       </c>
-      <c r="H5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" t="s">
-        <v>32</v>
-      </c>
-      <c r="L5" t="s">
-        <v>21</v>
-      </c>
-      <c r="M5" t="s">
+      <c r="J22" t="s">
+        <v>22</v>
+      </c>
+      <c r="L22" t="s">
+        <v>134</v>
+      </c>
+      <c r="M22" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="N22" t="s">
+        <v>25</v>
+      </c>
+      <c r="O22" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" t="s">
+        <v>136</v>
+      </c>
+      <c r="D23" t="s">
+        <v>137</v>
+      </c>
+      <c r="E23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="1">
+        <v>46275</v>
+      </c>
+      <c r="G23" t="s">
+        <v>138</v>
+      </c>
+      <c r="H23" s="2">
+        <v>261950</v>
+      </c>
+      <c r="I23" s="2">
+        <v>403</v>
+      </c>
+      <c r="J23" t="s">
+        <v>22</v>
+      </c>
+      <c r="L23" t="s">
+        <v>139</v>
+      </c>
+      <c r="N23" t="s">
+        <v>25</v>
+      </c>
+      <c r="O23" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" t="s">
         <v>35</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C24" t="s">
+        <v>48</v>
+      </c>
+      <c r="D24" t="s">
+        <v>141</v>
+      </c>
+      <c r="E24" t="s">
+        <v>20</v>
+      </c>
+      <c r="F24" s="1">
+        <v>46275</v>
+      </c>
+      <c r="G24" t="s">
+        <v>50</v>
+      </c>
+      <c r="H24" s="2">
+        <v>702000</v>
+      </c>
+      <c r="I24" s="2">
+        <v>1080</v>
+      </c>
+      <c r="J24" t="s">
+        <v>22</v>
+      </c>
+      <c r="K24" t="s">
+        <v>142</v>
+      </c>
+      <c r="L24" t="s">
+        <v>143</v>
+      </c>
+      <c r="N24" t="s">
+        <v>25</v>
+      </c>
+      <c r="O24" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="1">
-        <v>46267</v>
-      </c>
-      <c r="E6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" s="2">
-        <v>327600</v>
-      </c>
-      <c r="G6" s="2">
-        <v>504</v>
-      </c>
-      <c r="H6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J6" t="s">
-        <v>37</v>
-      </c>
-      <c r="K6" t="s">
-        <v>38</v>
-      </c>
-      <c r="L6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="1">
-        <v>46268</v>
-      </c>
-      <c r="E7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" s="2">
-        <v>152750</v>
-      </c>
-      <c r="G7" s="2">
-        <v>235</v>
-      </c>
-      <c r="H7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I7" t="s">
-        <v>43</v>
-      </c>
-      <c r="J7" t="s">
-        <v>44</v>
-      </c>
-      <c r="L7" t="s">
-        <v>21</v>
-      </c>
-      <c r="M7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="1">
-        <v>46268</v>
-      </c>
-      <c r="E8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" s="2">
-        <v>190300</v>
-      </c>
-      <c r="G8" s="2">
-        <v>173</v>
-      </c>
-      <c r="H8" t="s">
-        <v>18</v>
-      </c>
-      <c r="J8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K8" t="s">
+      <c r="B25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" t="s">
+        <v>145</v>
+      </c>
+      <c r="D25" t="s">
+        <v>146</v>
+      </c>
+      <c r="E25" t="s">
+        <v>20</v>
+      </c>
+      <c r="F25" s="1">
+        <v>46275</v>
+      </c>
+      <c r="G25" t="s">
         <v>50</v>
       </c>
-      <c r="L8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="1">
-        <v>46269</v>
-      </c>
-      <c r="E9" t="s">
-        <v>54</v>
-      </c>
-      <c r="F9" s="2">
-        <v>1409100</v>
-      </c>
-      <c r="G9" s="2">
-        <v>1281</v>
-      </c>
-      <c r="H9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J9" t="s">
-        <v>55</v>
-      </c>
-      <c r="L9" t="s">
-        <v>21</v>
-      </c>
-      <c r="M9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>57</v>
-      </c>
-      <c r="B10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="1">
-        <v>46270</v>
-      </c>
-      <c r="E10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F10" s="2">
-        <v>568100</v>
-      </c>
-      <c r="G10" s="2">
-        <v>874</v>
-      </c>
-      <c r="H10" t="s">
-        <v>18</v>
-      </c>
-      <c r="I10" t="s">
-        <v>60</v>
-      </c>
-      <c r="J10" t="s">
-        <v>61</v>
-      </c>
-      <c r="K10" t="s">
-        <v>62</v>
-      </c>
-      <c r="L10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M10" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>64</v>
-      </c>
-      <c r="B11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="1">
-        <v>46272</v>
-      </c>
-      <c r="E11" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" s="2">
-        <v>98800</v>
-      </c>
-      <c r="G11" s="2">
-        <v>152</v>
-      </c>
-      <c r="H11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J11" t="s">
-        <v>66</v>
-      </c>
-      <c r="K11" t="s">
-        <v>27</v>
-      </c>
-      <c r="L11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M11" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>68</v>
-      </c>
-      <c r="B12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="1">
-        <v>46272</v>
-      </c>
-      <c r="E12" t="s">
-        <v>70</v>
-      </c>
-      <c r="F12" s="2">
-        <v>112600</v>
-      </c>
-      <c r="G12" s="2">
-        <v>173.23076923076923</v>
-      </c>
-      <c r="H12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J12" t="s">
-        <v>71</v>
-      </c>
-      <c r="L12" t="s">
-        <v>21</v>
-      </c>
-      <c r="M12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>73</v>
-      </c>
-      <c r="B13" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="1">
-        <v>46272</v>
-      </c>
-      <c r="E13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F13" s="2">
-        <v>346450</v>
-      </c>
-      <c r="G13" s="2">
-        <v>533</v>
-      </c>
-      <c r="H13" t="s">
-        <v>18</v>
-      </c>
-      <c r="I13" t="s">
-        <v>76</v>
-      </c>
-      <c r="J13" t="s">
-        <v>77</v>
-      </c>
-      <c r="L13" t="s">
-        <v>21</v>
-      </c>
-      <c r="M13" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>79</v>
-      </c>
-      <c r="B14" t="s">
-        <v>80</v>
-      </c>
-      <c r="C14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="1">
-        <v>46272</v>
-      </c>
-      <c r="E14" t="s">
-        <v>17</v>
-      </c>
-      <c r="F14" s="2">
-        <v>5230550</v>
-      </c>
-      <c r="G14" s="2">
-        <v>8047</v>
-      </c>
-      <c r="H14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J14" t="s">
-        <v>81</v>
-      </c>
-      <c r="L14" t="s">
-        <v>21</v>
-      </c>
-      <c r="M14" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>83</v>
-      </c>
-      <c r="B15" t="s">
-        <v>84</v>
-      </c>
-      <c r="C15" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" s="1">
-        <v>46272</v>
-      </c>
-      <c r="E15" t="s">
-        <v>85</v>
-      </c>
-      <c r="F15" s="2">
-        <v>2956800</v>
-      </c>
-      <c r="G15" s="2">
-        <v>2688</v>
-      </c>
-      <c r="H15" t="s">
-        <v>18</v>
-      </c>
-      <c r="J15" t="s">
-        <v>86</v>
-      </c>
-      <c r="K15" t="s">
-        <v>87</v>
-      </c>
-      <c r="L15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M15" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>89</v>
-      </c>
-      <c r="B16" t="s">
-        <v>90</v>
-      </c>
-      <c r="C16" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" s="1">
-        <v>46273</v>
-      </c>
-      <c r="E16" t="s">
-        <v>91</v>
-      </c>
-      <c r="F16" s="2">
-        <v>4514400</v>
-      </c>
-      <c r="G16" s="2">
-        <v>4104</v>
-      </c>
-      <c r="H16" t="s">
-        <v>18</v>
-      </c>
-      <c r="I16" t="s">
-        <v>92</v>
-      </c>
-      <c r="J16" t="s">
-        <v>93</v>
-      </c>
-      <c r="K16" t="s">
-        <v>94</v>
-      </c>
-      <c r="L16" t="s">
-        <v>21</v>
-      </c>
-      <c r="M16" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>96</v>
-      </c>
-      <c r="B17" t="s">
-        <v>97</v>
-      </c>
-      <c r="C17" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" s="1">
-        <v>46273</v>
-      </c>
-      <c r="E17" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="2">
-        <v>318500</v>
-      </c>
-      <c r="G17" s="2">
-        <v>490</v>
-      </c>
-      <c r="H17" t="s">
-        <v>18</v>
-      </c>
-      <c r="I17" t="s">
-        <v>98</v>
-      </c>
-      <c r="J17" t="s">
-        <v>99</v>
-      </c>
-      <c r="K17" t="s">
-        <v>27</v>
-      </c>
-      <c r="L17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M17" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>101</v>
-      </c>
-      <c r="B18" t="s">
-        <v>102</v>
-      </c>
-      <c r="C18" t="s">
-        <v>16</v>
-      </c>
-      <c r="D18" s="1">
-        <v>46274</v>
-      </c>
-      <c r="E18" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" s="2">
-        <v>207350</v>
-      </c>
-      <c r="G18" s="2">
-        <v>319</v>
-      </c>
-      <c r="H18" t="s">
-        <v>18</v>
-      </c>
-      <c r="J18" t="s">
-        <v>103</v>
-      </c>
-      <c r="K18" t="s">
-        <v>27</v>
-      </c>
-      <c r="L18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M18" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>105</v>
-      </c>
-      <c r="B19" t="s">
-        <v>106</v>
-      </c>
-      <c r="C19" t="s">
-        <v>16</v>
-      </c>
-      <c r="D19" s="1">
-        <v>46274</v>
-      </c>
-      <c r="E19" t="s">
-        <v>107</v>
-      </c>
-      <c r="F19" s="2">
-        <v>112450</v>
-      </c>
-      <c r="G19" s="2">
-        <v>173</v>
-      </c>
-      <c r="H19" t="s">
-        <v>18</v>
-      </c>
-      <c r="I19" t="s">
-        <v>108</v>
-      </c>
-      <c r="J19" t="s">
-        <v>109</v>
-      </c>
-      <c r="K19" t="s">
-        <v>110</v>
-      </c>
-      <c r="L19" t="s">
-        <v>21</v>
-      </c>
-      <c r="M19" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>64</v>
-      </c>
-      <c r="B20" t="s">
-        <v>74</v>
-      </c>
-      <c r="C20" t="s">
-        <v>16</v>
-      </c>
-      <c r="D20" s="1">
-        <v>46274</v>
-      </c>
-      <c r="E20" t="s">
-        <v>75</v>
-      </c>
-      <c r="F20" s="2">
-        <v>185900</v>
-      </c>
-      <c r="G20" s="2">
-        <v>286</v>
-      </c>
-      <c r="H20" t="s">
-        <v>18</v>
-      </c>
-      <c r="I20" t="s">
-        <v>76</v>
-      </c>
-      <c r="J20" t="s">
-        <v>112</v>
-      </c>
-      <c r="K20" t="s">
-        <v>113</v>
-      </c>
-      <c r="L20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M20" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>115</v>
-      </c>
-      <c r="B21" t="s">
-        <v>116</v>
-      </c>
-      <c r="C21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D21" s="1">
-        <v>46275</v>
-      </c>
-      <c r="E21" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" s="2">
-        <v>261950</v>
-      </c>
-      <c r="G21" s="2">
-        <v>403</v>
-      </c>
-      <c r="H21" t="s">
-        <v>18</v>
-      </c>
-      <c r="I21" t="s">
-        <v>117</v>
-      </c>
-      <c r="J21" t="s">
-        <v>118</v>
-      </c>
-      <c r="K21" t="s">
-        <v>27</v>
-      </c>
-      <c r="L21" t="s">
-        <v>21</v>
-      </c>
-      <c r="M21" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>120</v>
-      </c>
-      <c r="B22" t="s">
-        <v>121</v>
-      </c>
-      <c r="C22" t="s">
-        <v>16</v>
-      </c>
-      <c r="D22" s="1">
-        <v>46275</v>
-      </c>
-      <c r="E22" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" s="2">
-        <v>112450</v>
-      </c>
-      <c r="G22" s="2">
-        <v>173</v>
-      </c>
-      <c r="H22" t="s">
-        <v>18</v>
-      </c>
-      <c r="J22" t="s">
-        <v>122</v>
-      </c>
-      <c r="K22" t="s">
-        <v>27</v>
-      </c>
-      <c r="L22" t="s">
-        <v>21</v>
-      </c>
-      <c r="M22" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>124</v>
-      </c>
-      <c r="B23" t="s">
-        <v>125</v>
-      </c>
-      <c r="C23" t="s">
-        <v>16</v>
-      </c>
-      <c r="D23" s="1">
-        <v>46275</v>
-      </c>
-      <c r="E23" t="s">
-        <v>126</v>
-      </c>
-      <c r="F23" s="2">
-        <v>261950</v>
-      </c>
-      <c r="G23" s="2">
-        <v>403</v>
-      </c>
-      <c r="H23" t="s">
-        <v>18</v>
-      </c>
-      <c r="J23" t="s">
-        <v>127</v>
-      </c>
-      <c r="L23" t="s">
-        <v>21</v>
-      </c>
-      <c r="M23" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>40</v>
-      </c>
-      <c r="B24" t="s">
-        <v>129</v>
-      </c>
-      <c r="C24" t="s">
-        <v>16</v>
-      </c>
-      <c r="D24" s="1">
-        <v>46275</v>
-      </c>
-      <c r="E24" t="s">
-        <v>42</v>
-      </c>
-      <c r="F24" s="2">
-        <v>702000</v>
-      </c>
-      <c r="G24" s="2">
-        <v>1080</v>
-      </c>
-      <c r="H24" t="s">
-        <v>18</v>
-      </c>
-      <c r="I24" t="s">
-        <v>130</v>
-      </c>
-      <c r="J24" t="s">
-        <v>131</v>
-      </c>
-      <c r="L24" t="s">
-        <v>21</v>
-      </c>
-      <c r="M24" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>133</v>
-      </c>
-      <c r="B25" t="s">
-        <v>134</v>
-      </c>
-      <c r="C25" t="s">
-        <v>16</v>
-      </c>
-      <c r="D25" s="1">
-        <v>46275</v>
-      </c>
-      <c r="E25" t="s">
-        <v>42</v>
-      </c>
-      <c r="F25" s="2">
+      <c r="H25" s="2">
         <v>852150</v>
       </c>
-      <c r="G25" s="2">
+      <c r="I25" s="2">
         <v>1311</v>
       </c>
-      <c r="H25" t="s">
-        <v>18</v>
-      </c>
       <c r="J25" t="s">
-        <v>135</v>
+        <v>22</v>
       </c>
       <c r="L25" t="s">
-        <v>21</v>
-      </c>
-      <c r="M25" t="s">
-        <v>136</v>
+        <v>147</v>
+      </c>
+      <c r="N25" t="s">
+        <v>25</v>
+      </c>
+      <c r="O25" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A1:O1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
